--- a/Assets/Excel/StateMachineConfig.xlsx
+++ b/Assets/Excel/StateMachineConfig.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\computer\project\Unity_ARPG_DEMO\Assets\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23820" windowHeight="11720"/>
+    <workbookView windowWidth="22970" windowHeight="11720"/>
   </bookViews>
   <sheets>
     <sheet name="state" sheetId="1" r:id="rId1"/>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="75">
   <si>
     <t>CharacterId</t>
   </si>
@@ -51,6 +56,15 @@
   </si>
   <si>
     <t>OnAtk</t>
+  </si>
+  <si>
+    <t>OnSkill</t>
+  </si>
+  <si>
+    <t>OnEnhanceSkill</t>
+  </si>
+  <si>
+    <t>UnlockEnhance</t>
   </si>
   <si>
     <t>int</t>
@@ -95,6 +109,17 @@
 目标状态 ID</t>
   </si>
   <si>
+    <t>当进行技能</t>
+  </si>
+  <si>
+    <t>当进行强化技能
+前摇后摇和Skill一致
+[离场状态,入场状态]</t>
+  </si>
+  <si>
+    <t>是否解锁强化效果</t>
+  </si>
+  <si>
     <t>移动</t>
   </si>
   <si>
@@ -104,6 +129,12 @@
     <t>1;1;10021</t>
   </si>
   <si>
+    <t>1;1;20021</t>
+  </si>
+  <si>
+    <t>10034;20034</t>
+  </si>
+  <si>
     <t>普通攻击1</t>
   </si>
   <si>
@@ -125,6 +156,9 @@
     <t>1;1;10023</t>
   </si>
   <si>
+    <t>1;1;20032</t>
+  </si>
+  <si>
     <t>普通攻击3</t>
   </si>
   <si>
@@ -138,6 +172,99 @@
   </si>
   <si>
     <t>Attack_04</t>
+  </si>
+  <si>
+    <t>技能攻击1</t>
+  </si>
+  <si>
+    <t>Skill_01</t>
+  </si>
+  <si>
+    <t>技能攻击2</t>
+  </si>
+  <si>
+    <t>Skill_02</t>
+  </si>
+  <si>
+    <t>技能攻击3</t>
+  </si>
+  <si>
+    <t>Skill_03</t>
+  </si>
+  <si>
+    <t>技能攻击4</t>
+  </si>
+  <si>
+    <t>Skill_04</t>
+  </si>
+  <si>
+    <t>机甲待机</t>
+  </si>
+  <si>
+    <t>Stand_Mech</t>
+  </si>
+  <si>
+    <t>20033;10033</t>
+  </si>
+  <si>
+    <t>机甲攻击1</t>
+  </si>
+  <si>
+    <t>Attack_Mech_01</t>
+  </si>
+  <si>
+    <t>1;1;20022</t>
+  </si>
+  <si>
+    <t>机甲攻击2</t>
+  </si>
+  <si>
+    <t>Attack_Mech_02</t>
+  </si>
+  <si>
+    <t>1;1;20023</t>
+  </si>
+  <si>
+    <t>1;1;10031</t>
+  </si>
+  <si>
+    <t>机甲攻击3</t>
+  </si>
+  <si>
+    <t>Attack_Mech_03</t>
+  </si>
+  <si>
+    <t>1;1;20024</t>
+  </si>
+  <si>
+    <t>机甲攻击4</t>
+  </si>
+  <si>
+    <t>Attack_Mech_04</t>
+  </si>
+  <si>
+    <t>机甲技能1</t>
+  </si>
+  <si>
+    <t>Skill_Mech_01</t>
+  </si>
+  <si>
+    <t>机甲技能2</t>
+  </si>
+  <si>
+    <t>Skill_Mech_02</t>
+  </si>
+  <si>
+    <t>机甲技能3</t>
+  </si>
+  <si>
+    <t>Skill_Mech_03</t>
+  </si>
+  <si>
+    <t>机甲技能4</t>
+  </si>
+  <si>
+    <t>Skill_Mech_04</t>
   </si>
 </sst>
 </file>
@@ -751,7 +878,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -761,6 +888,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1108,22 +1238,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="7"/>
+  <dimension ref="A1:K21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="16.2727272727273" customWidth="1"/>
     <col min="2" max="2" width="18.5454545454545" customWidth="1"/>
     <col min="3" max="4" width="10.6363636363636" customWidth="1"/>
-    <col min="5" max="5" width="15.1818181818182" customWidth="1"/>
+    <col min="5" max="5" width="16.2727272727273" customWidth="1"/>
     <col min="6" max="6" width="28.6363636363636" customWidth="1"/>
     <col min="7" max="7" width="33" customWidth="1"/>
     <col min="8" max="8" width="29.6363636363636" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="9" max="9" width="15.8909090909091" customWidth="1"/>
     <col min="10" max="10" width="20.8181818181818" customWidth="1"/>
     <col min="11" max="11" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1148,60 +1278,87 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="56" customHeight="1" spans="1:8">
+        <v>14</v>
+      </c>
+      <c r="I2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="56" customHeight="1" spans="1:11">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>22</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4">
         <v>1001</v>
       </c>
@@ -1212,16 +1369,22 @@
         <v>1001</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>28</v>
+      </c>
+      <c r="I4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5">
         <v>1001</v>
       </c>
@@ -1232,22 +1395,28 @@
         <v>10021</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F5">
         <v>1001</v>
       </c>
       <c r="G5" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="H5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>34</v>
+      </c>
+      <c r="I5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6">
         <v>1001</v>
       </c>
@@ -1258,22 +1427,28 @@
         <v>10022</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F6">
         <v>1001</v>
       </c>
       <c r="G6" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="H6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>37</v>
+      </c>
+      <c r="I6" t="s">
+        <v>38</v>
+      </c>
+      <c r="J6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7">
         <v>1001</v>
       </c>
@@ -1284,22 +1459,28 @@
         <v>10023</v>
       </c>
       <c r="D7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7">
+        <v>1001</v>
+      </c>
+      <c r="G7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7" t="s">
+        <v>41</v>
+      </c>
+      <c r="I7" t="s">
+        <v>38</v>
+      </c>
+      <c r="J7" t="s">
         <v>30</v>
       </c>
-      <c r="E7" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7">
-        <v>1001</v>
-      </c>
-      <c r="G7" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8">
         <v>1001</v>
       </c>
@@ -1310,19 +1491,351 @@
         <v>10024</v>
       </c>
       <c r="D8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8">
+        <v>1001</v>
+      </c>
+      <c r="G8" t="s">
         <v>33</v>
       </c>
-      <c r="E8" t="s">
+      <c r="H8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I8" t="s">
+        <v>38</v>
+      </c>
+      <c r="J8" t="s">
+        <v>30</v>
+      </c>
+      <c r="K8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9">
+        <v>1001</v>
+      </c>
+      <c r="B9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>10031</v>
+      </c>
+      <c r="D9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9">
+        <v>1001</v>
+      </c>
+      <c r="G9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9" t="s">
         <v>34</v>
       </c>
-      <c r="F8">
-        <v>1001</v>
-      </c>
-      <c r="G8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" t="s">
-        <v>22</v>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10">
+        <v>1001</v>
+      </c>
+      <c r="B10" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>10032</v>
+      </c>
+      <c r="D10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10">
+        <v>1001</v>
+      </c>
+      <c r="G10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11">
+        <v>1001</v>
+      </c>
+      <c r="B11" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>10033</v>
+      </c>
+      <c r="D11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11">
+        <v>1001</v>
+      </c>
+      <c r="G11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12">
+        <v>1001</v>
+      </c>
+      <c r="B12" t="b">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>10034</v>
+      </c>
+      <c r="D12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12">
+        <v>1001</v>
+      </c>
+      <c r="G12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13">
+        <v>1001</v>
+      </c>
+      <c r="B13" t="b">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>2001</v>
+      </c>
+      <c r="D13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" t="s">
+        <v>53</v>
+      </c>
+      <c r="H13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I13" t="s">
+        <v>28</v>
+      </c>
+      <c r="J13" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14">
+        <v>1001</v>
+      </c>
+      <c r="B14" t="b">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>20021</v>
+      </c>
+      <c r="D14" t="s">
+        <v>55</v>
+      </c>
+      <c r="E14" t="s">
+        <v>56</v>
+      </c>
+      <c r="F14">
+        <v>2001</v>
+      </c>
+      <c r="H14" t="s">
+        <v>57</v>
+      </c>
+      <c r="I14" t="s">
+        <v>28</v>
+      </c>
+      <c r="J14" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15">
+        <v>1001</v>
+      </c>
+      <c r="B15" t="b">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>20022</v>
+      </c>
+      <c r="D15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15">
+        <v>2001</v>
+      </c>
+      <c r="H15" t="s">
+        <v>60</v>
+      </c>
+      <c r="I15" t="s">
+        <v>61</v>
+      </c>
+      <c r="J15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16">
+        <v>1001</v>
+      </c>
+      <c r="B16" t="b">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>20023</v>
+      </c>
+      <c r="D16" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F16">
+        <v>2001</v>
+      </c>
+      <c r="H16" t="s">
+        <v>64</v>
+      </c>
+      <c r="I16" t="s">
+        <v>61</v>
+      </c>
+      <c r="J16" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17">
+        <v>1001</v>
+      </c>
+      <c r="B17" t="b">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>20024</v>
+      </c>
+      <c r="D17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E17" t="s">
+        <v>66</v>
+      </c>
+      <c r="F17">
+        <v>2001</v>
+      </c>
+      <c r="H17" t="s">
+        <v>29</v>
+      </c>
+      <c r="I17" t="s">
+        <v>61</v>
+      </c>
+      <c r="J17" t="s">
+        <v>54</v>
+      </c>
+      <c r="K17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18">
+        <v>1001</v>
+      </c>
+      <c r="B18" t="b">
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <v>20031</v>
+      </c>
+      <c r="D18" t="s">
+        <v>67</v>
+      </c>
+      <c r="E18" t="s">
+        <v>68</v>
+      </c>
+      <c r="F18">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19">
+        <v>1001</v>
+      </c>
+      <c r="B19" t="b">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>20032</v>
+      </c>
+      <c r="D19" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F19">
+        <v>2001</v>
+      </c>
+      <c r="H19" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20">
+        <v>1001</v>
+      </c>
+      <c r="B20" t="b">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>20033</v>
+      </c>
+      <c r="D20" t="s">
+        <v>71</v>
+      </c>
+      <c r="E20" t="s">
+        <v>72</v>
+      </c>
+      <c r="F20">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21">
+        <v>1001</v>
+      </c>
+      <c r="B21" t="b">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>20034</v>
+      </c>
+      <c r="D21" t="s">
+        <v>73</v>
+      </c>
+      <c r="E21" t="s">
+        <v>74</v>
+      </c>
+      <c r="F21">
+        <v>2001</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excel/StateMachineConfig.xlsx
+++ b/Assets/Excel/StateMachineConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="77">
   <si>
     <t>CharacterId</t>
   </si>
@@ -65,6 +65,9 @@
   </si>
   <si>
     <t>UnlockEnhance</t>
+  </si>
+  <si>
+    <t>OnSprint</t>
   </si>
   <si>
     <t>int</t>
@@ -118,6 +121,9 @@
   </si>
   <si>
     <t>是否解锁强化效果</t>
+  </si>
+  <si>
+    <t>当进行冲刺</t>
   </si>
   <si>
     <t>移动</t>
@@ -1238,7 +1244,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="16.2727272727273" customWidth="1"/>
@@ -1251,9 +1257,10 @@
     <col min="9" max="9" width="15.8909090909091" customWidth="1"/>
     <col min="10" max="10" width="20.8181818181818" customWidth="1"/>
     <col min="11" max="11" width="23" customWidth="1"/>
+    <col min="12" max="12" width="11.8181818181818" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1287,78 +1294,87 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
       <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" t="s">
         <v>13</v>
       </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="56" customHeight="1" spans="1:11">
+      <c r="L2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="56" customHeight="1" spans="1:12">
       <c r="A3" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+        <v>26</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4">
         <v>1001</v>
       </c>
@@ -1369,22 +1385,22 @@
         <v>1001</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5">
         <v>1001</v>
       </c>
@@ -1395,28 +1411,28 @@
         <v>10021</v>
       </c>
       <c r="D5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5">
+        <v>1001</v>
+      </c>
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" t="s">
         <v>31</v>
       </c>
-      <c r="E5" t="s">
+      <c r="J5" t="s">
         <v>32</v>
       </c>
-      <c r="F5">
-        <v>1001</v>
-      </c>
-      <c r="G5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6">
         <v>1001</v>
       </c>
@@ -1427,28 +1443,28 @@
         <v>10022</v>
       </c>
       <c r="D6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6">
+        <v>1001</v>
+      </c>
+      <c r="G6" t="s">
         <v>35</v>
       </c>
-      <c r="E6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6">
-        <v>1001</v>
-      </c>
-      <c r="G6" t="s">
-        <v>33</v>
-      </c>
       <c r="H6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7">
         <v>1001</v>
       </c>
@@ -1459,28 +1475,28 @@
         <v>10023</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7">
+        <v>1001</v>
+      </c>
+      <c r="G7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" t="s">
+        <v>43</v>
+      </c>
+      <c r="I7" t="s">
         <v>40</v>
       </c>
-      <c r="F7">
-        <v>1001</v>
-      </c>
-      <c r="G7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H7" t="s">
-        <v>41</v>
-      </c>
-      <c r="I7" t="s">
-        <v>38</v>
-      </c>
       <c r="J7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8">
         <v>1001</v>
       </c>
@@ -1491,31 +1507,31 @@
         <v>10024</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F8">
         <v>1001</v>
       </c>
       <c r="G8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K8" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:12">
       <c r="A9">
         <v>1001</v>
       </c>
@@ -1526,22 +1542,22 @@
         <v>10031</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F9">
         <v>1001</v>
       </c>
       <c r="G9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H9" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10">
         <v>1001</v>
       </c>
@@ -1552,19 +1568,19 @@
         <v>10032</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F10">
         <v>1001</v>
       </c>
       <c r="G10" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11">
         <v>1001</v>
       </c>
@@ -1575,19 +1591,22 @@
         <v>10033</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F11">
         <v>1001</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+        <v>35</v>
+      </c>
+      <c r="H11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12">
         <v>1001</v>
       </c>
@@ -1598,19 +1617,19 @@
         <v>10034</v>
       </c>
       <c r="D12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E12" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F12">
         <v>1001</v>
       </c>
       <c r="G12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13">
         <v>1001</v>
       </c>
@@ -1621,22 +1640,22 @@
         <v>2001</v>
       </c>
       <c r="D13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I13" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J13" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14">
         <v>1001</v>
       </c>
@@ -1647,25 +1666,25 @@
         <v>20021</v>
       </c>
       <c r="D14" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F14">
         <v>2001</v>
       </c>
       <c r="H14" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I14" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J14" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15">
         <v>1001</v>
       </c>
@@ -1676,25 +1695,25 @@
         <v>20022</v>
       </c>
       <c r="D15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E15" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F15">
         <v>2001</v>
       </c>
       <c r="H15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J15" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16">
         <v>1001</v>
       </c>
@@ -1705,22 +1724,22 @@
         <v>20023</v>
       </c>
       <c r="D16" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E16" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F16">
         <v>2001</v>
       </c>
       <c r="H16" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I16" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J16" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1734,22 +1753,22 @@
         <v>20024</v>
       </c>
       <c r="D17" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E17" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F17">
         <v>2001</v>
       </c>
       <c r="H17" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I17" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K17" t="b">
         <v>1</v>
@@ -1766,10 +1785,10 @@
         <v>20031</v>
       </c>
       <c r="D18" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E18" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F18">
         <v>2001</v>
@@ -1786,16 +1805,16 @@
         <v>20032</v>
       </c>
       <c r="D19" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E19" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F19">
         <v>2001</v>
       </c>
       <c r="H19" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1809,10 +1828,10 @@
         <v>20033</v>
       </c>
       <c r="D20" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E20" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F20">
         <v>2001</v>
@@ -1829,13 +1848,16 @@
         <v>20034</v>
       </c>
       <c r="D21" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E21" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F21">
         <v>2001</v>
+      </c>
+      <c r="H21" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excel/StateMachineConfig.xlsx
+++ b/Assets/Excel/StateMachineConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="106">
   <si>
     <t>CharacterId</t>
   </si>
@@ -68,6 +68,15 @@
   </si>
   <si>
     <t>OnSprint</t>
+  </si>
+  <si>
+    <t>OnJump</t>
+  </si>
+  <si>
+    <t>OnFalling</t>
+  </si>
+  <si>
+    <t>OnLand</t>
   </si>
   <si>
     <t>int</t>
@@ -127,6 +136,15 @@
     <t>当进行冲刺</t>
   </si>
   <si>
+    <t>当进行跳跃</t>
+  </si>
+  <si>
+    <t>当滞空时</t>
+  </si>
+  <si>
+    <t>当落地时</t>
+  </si>
+  <si>
     <t>移动</t>
   </si>
   <si>
@@ -142,7 +160,10 @@
     <t>10034;20034</t>
   </si>
   <si>
-    <t>0;1;</t>
+    <t>0;1;1004</t>
+  </si>
+  <si>
+    <t>0;1;10051</t>
   </si>
   <si>
     <t>普通攻击1</t>
@@ -212,6 +233,54 @@
   </si>
   <si>
     <t>Sprint</t>
+  </si>
+  <si>
+    <t>0.3;1;1001</t>
+  </si>
+  <si>
+    <t>走跳跃</t>
+  </si>
+  <si>
+    <t>Jump_Walk</t>
+  </si>
+  <si>
+    <t>0.68;1;10053</t>
+  </si>
+  <si>
+    <t>跑跳跃</t>
+  </si>
+  <si>
+    <t>Jump_Run</t>
+  </si>
+  <si>
+    <t>跳跃循环</t>
+  </si>
+  <si>
+    <t>Jump_Loop</t>
+  </si>
+  <si>
+    <t>0;1;10054</t>
+  </si>
+  <si>
+    <t>跳跃轻落地</t>
+  </si>
+  <si>
+    <t>Jump_Light_Land</t>
+  </si>
+  <si>
+    <t>0.05;1;10051</t>
+  </si>
+  <si>
+    <t>跳跃重落地</t>
+  </si>
+  <si>
+    <t>Jump_Heavy_Land</t>
+  </si>
+  <si>
+    <t>跳跃翻滚落地</t>
+  </si>
+  <si>
+    <t>Jump_Roll_Land</t>
   </si>
   <si>
     <t>机甲待机</t>
@@ -1263,12 +1332,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:O29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="16.2727272727273" customWidth="1"/>
     <col min="2" max="2" width="18.5454545454545" customWidth="1"/>
-    <col min="3" max="4" width="10.6363636363636" customWidth="1"/>
+    <col min="3" max="3" width="10.6363636363636" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="16.2727272727273" customWidth="1"/>
     <col min="6" max="6" width="28.6363636363636" customWidth="1"/>
     <col min="7" max="7" width="33" customWidth="1"/>
@@ -1277,9 +1347,11 @@
     <col min="10" max="10" width="20.8181818181818" customWidth="1"/>
     <col min="11" max="11" width="23" customWidth="1"/>
     <col min="12" max="12" width="11.8181818181818" customWidth="1"/>
+    <col min="13" max="14" width="14" customWidth="1"/>
+    <col min="15" max="15" width="10.6363636363636" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1316,84 +1388,111 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="56" customHeight="1" spans="1:12">
+        <v>18</v>
+      </c>
+      <c r="M2" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="56" customHeight="1" spans="1:15">
       <c r="A3" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+        <v>30</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4">
         <v>1001</v>
       </c>
@@ -1404,25 +1503,28 @@
         <v>1001</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="J4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="L4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+        <v>39</v>
+      </c>
+      <c r="M4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5">
         <v>1001</v>
       </c>
@@ -1433,28 +1535,34 @@
         <v>10021</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E5" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="F5">
         <v>1001</v>
       </c>
       <c r="G5" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="H5" t="s">
+        <v>44</v>
+      </c>
+      <c r="I5" t="s">
         <v>37</v>
       </c>
-      <c r="I5" t="s">
-        <v>31</v>
-      </c>
       <c r="J5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+        <v>38</v>
+      </c>
+      <c r="L5" t="s">
+        <v>39</v>
+      </c>
+      <c r="M5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6">
         <v>1001</v>
       </c>
@@ -1465,28 +1573,34 @@
         <v>10022</v>
       </c>
       <c r="D6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6">
+        <v>1001</v>
+      </c>
+      <c r="G6" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" t="s">
+        <v>47</v>
+      </c>
+      <c r="I6" t="s">
+        <v>48</v>
+      </c>
+      <c r="J6" t="s">
         <v>38</v>
       </c>
-      <c r="E6" t="s">
+      <c r="L6" t="s">
         <v>39</v>
       </c>
-      <c r="F6">
-        <v>1001</v>
-      </c>
-      <c r="G6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="M6" t="s">
         <v>40</v>
       </c>
-      <c r="I6" t="s">
-        <v>41</v>
-      </c>
-      <c r="J6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7">
         <v>1001</v>
       </c>
@@ -1497,28 +1611,34 @@
         <v>10023</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="E7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7">
+        <v>1001</v>
+      </c>
+      <c r="G7" t="s">
         <v>43</v>
       </c>
-      <c r="F7">
-        <v>1001</v>
-      </c>
-      <c r="G7" t="s">
-        <v>36</v>
-      </c>
       <c r="H7" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="I7" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="J7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+        <v>38</v>
+      </c>
+      <c r="L7" t="s">
+        <v>39</v>
+      </c>
+      <c r="M7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8">
         <v>1001</v>
       </c>
@@ -1529,31 +1649,37 @@
         <v>10024</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="E8" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="F8">
         <v>1001</v>
       </c>
       <c r="G8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" t="s">
         <v>36</v>
       </c>
-      <c r="H8" t="s">
-        <v>30</v>
-      </c>
       <c r="I8" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="J8" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="K8" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:12">
+      <c r="L8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9">
         <v>1001</v>
       </c>
@@ -1564,22 +1690,22 @@
         <v>10031</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="E9" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F9">
         <v>1001</v>
       </c>
       <c r="G9" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="H9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10">
         <v>1001</v>
       </c>
@@ -1590,19 +1716,19 @@
         <v>10032</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E10" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F10">
         <v>1001</v>
       </c>
       <c r="G10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11">
         <v>1001</v>
       </c>
@@ -1613,22 +1739,22 @@
         <v>10033</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="E11" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F11">
         <v>1001</v>
       </c>
       <c r="G11" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="H11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12">
         <v>1001</v>
       </c>
@@ -1639,19 +1765,19 @@
         <v>10034</v>
       </c>
       <c r="D12" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="E12" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="F12">
         <v>1001</v>
       </c>
       <c r="G12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13">
         <v>1001</v>
       </c>
@@ -1662,13 +1788,19 @@
         <v>1004</v>
       </c>
       <c r="D13" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E13" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
+        <v>63</v>
+      </c>
+      <c r="F13">
+        <v>1001</v>
+      </c>
+      <c r="G13" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14">
         <v>1001</v>
       </c>
@@ -1676,231 +1808,190 @@
         <v>0</v>
       </c>
       <c r="C14">
+        <v>10051</v>
+      </c>
+      <c r="D14" t="s">
+        <v>65</v>
+      </c>
+      <c r="E14" t="s">
+        <v>66</v>
+      </c>
+      <c r="F14"/>
+      <c r="N14" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15">
+        <v>1001</v>
+      </c>
+      <c r="B15" t="b">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>10052</v>
+      </c>
+      <c r="D15" t="s">
+        <v>68</v>
+      </c>
+      <c r="E15" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16">
+        <v>1001</v>
+      </c>
+      <c r="B16" t="b">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>10053</v>
+      </c>
+      <c r="D16" t="s">
+        <v>70</v>
+      </c>
+      <c r="E16" t="s">
+        <v>71</v>
+      </c>
+      <c r="O16" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17">
+        <v>1001</v>
+      </c>
+      <c r="B17" t="b">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>10054</v>
+      </c>
+      <c r="D17" t="s">
+        <v>73</v>
+      </c>
+      <c r="E17" t="s">
+        <v>74</v>
+      </c>
+      <c r="F17">
+        <v>1001</v>
+      </c>
+      <c r="G17" t="s">
+        <v>43</v>
+      </c>
+      <c r="M17" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18">
+        <v>1001</v>
+      </c>
+      <c r="B18" t="b">
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <v>10055</v>
+      </c>
+      <c r="D18" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18" t="s">
+        <v>77</v>
+      </c>
+      <c r="F18">
+        <v>1001</v>
+      </c>
+      <c r="G18" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19">
+        <v>1001</v>
+      </c>
+      <c r="B19" t="b">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>10056</v>
+      </c>
+      <c r="D19" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" t="s">
+        <v>79</v>
+      </c>
+      <c r="F19">
+        <v>1001</v>
+      </c>
+      <c r="G19" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20">
+        <v>1001</v>
+      </c>
+      <c r="B20" t="b">
+        <v>0</v>
+      </c>
+      <c r="C20">
         <v>2001</v>
       </c>
-      <c r="D14" t="s">
-        <v>57</v>
-      </c>
-      <c r="E14" t="s">
-        <v>58</v>
-      </c>
-      <c r="G14" t="s">
-        <v>59</v>
-      </c>
-      <c r="H14" t="s">
-        <v>31</v>
-      </c>
-      <c r="I14" t="s">
-        <v>30</v>
-      </c>
-      <c r="J14" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15">
-        <v>1001</v>
-      </c>
-      <c r="B15" t="b">
-        <v>0</v>
-      </c>
-      <c r="C15">
+      <c r="D20" t="s">
+        <v>80</v>
+      </c>
+      <c r="E20" t="s">
+        <v>81</v>
+      </c>
+      <c r="G20" t="s">
+        <v>82</v>
+      </c>
+      <c r="H20" t="s">
+        <v>37</v>
+      </c>
+      <c r="I20" t="s">
+        <v>36</v>
+      </c>
+      <c r="J20" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21">
+        <v>1001</v>
+      </c>
+      <c r="B21" t="b">
+        <v>0</v>
+      </c>
+      <c r="C21">
         <v>20021</v>
       </c>
-      <c r="D15" t="s">
-        <v>61</v>
-      </c>
-      <c r="E15" t="s">
-        <v>62</v>
-      </c>
-      <c r="F15">
-        <v>2001</v>
-      </c>
-      <c r="G15" t="s">
-        <v>59</v>
-      </c>
-      <c r="H15" t="s">
-        <v>63</v>
-      </c>
-      <c r="I15" t="s">
-        <v>30</v>
-      </c>
-      <c r="J15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="A16">
-        <v>1001</v>
-      </c>
-      <c r="B16" t="b">
-        <v>0</v>
-      </c>
-      <c r="C16">
-        <v>20022</v>
-      </c>
-      <c r="D16" t="s">
-        <v>64</v>
-      </c>
-      <c r="E16" t="s">
-        <v>65</v>
-      </c>
-      <c r="F16">
-        <v>2001</v>
-      </c>
-      <c r="G16" t="s">
-        <v>59</v>
-      </c>
-      <c r="H16" t="s">
-        <v>66</v>
-      </c>
-      <c r="I16" t="s">
-        <v>67</v>
-      </c>
-      <c r="J16" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17">
-        <v>1001</v>
-      </c>
-      <c r="B17" t="b">
-        <v>0</v>
-      </c>
-      <c r="C17">
-        <v>20023</v>
-      </c>
-      <c r="D17" t="s">
-        <v>68</v>
-      </c>
-      <c r="E17" t="s">
-        <v>69</v>
-      </c>
-      <c r="F17">
-        <v>2001</v>
-      </c>
-      <c r="G17" t="s">
-        <v>59</v>
-      </c>
-      <c r="H17" t="s">
-        <v>70</v>
-      </c>
-      <c r="I17" t="s">
-        <v>67</v>
-      </c>
-      <c r="J17" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18">
-        <v>1001</v>
-      </c>
-      <c r="B18" t="b">
-        <v>0</v>
-      </c>
-      <c r="C18">
-        <v>20024</v>
-      </c>
-      <c r="D18" t="s">
-        <v>71</v>
-      </c>
-      <c r="E18" t="s">
-        <v>72</v>
-      </c>
-      <c r="F18">
-        <v>2001</v>
-      </c>
-      <c r="G18" t="s">
-        <v>59</v>
-      </c>
-      <c r="H18" t="s">
-        <v>31</v>
-      </c>
-      <c r="I18" t="s">
-        <v>67</v>
-      </c>
-      <c r="J18" t="s">
-        <v>60</v>
-      </c>
-      <c r="K18" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19">
-        <v>1001</v>
-      </c>
-      <c r="B19" t="b">
-        <v>0</v>
-      </c>
-      <c r="C19">
-        <v>20031</v>
-      </c>
-      <c r="D19" t="s">
-        <v>73</v>
-      </c>
-      <c r="E19" t="s">
-        <v>74</v>
-      </c>
-      <c r="F19">
-        <v>2001</v>
-      </c>
-      <c r="G19" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20">
-        <v>1001</v>
-      </c>
-      <c r="B20" t="b">
-        <v>0</v>
-      </c>
-      <c r="C20">
-        <v>20032</v>
-      </c>
-      <c r="D20" t="s">
-        <v>75</v>
-      </c>
-      <c r="E20" t="s">
-        <v>76</v>
-      </c>
-      <c r="F20">
-        <v>2001</v>
-      </c>
-      <c r="G20" t="s">
-        <v>59</v>
-      </c>
-      <c r="H20" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21">
-        <v>1001</v>
-      </c>
-      <c r="B21" t="b">
-        <v>0</v>
-      </c>
-      <c r="C21">
-        <v>20033</v>
-      </c>
       <c r="D21" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="E21" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F21">
         <v>2001</v>
       </c>
       <c r="G21" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
+        <v>82</v>
+      </c>
+      <c r="H21" t="s">
+        <v>86</v>
+      </c>
+      <c r="I21" t="s">
+        <v>36</v>
+      </c>
+      <c r="J21" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22">
         <v>1001</v>
       </c>
@@ -1908,25 +1999,31 @@
         <v>0</v>
       </c>
       <c r="C22">
-        <v>20034</v>
+        <v>20022</v>
       </c>
       <c r="D22" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E22" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="F22">
         <v>2001</v>
       </c>
       <c r="G22" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="H22" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
+        <v>89</v>
+      </c>
+      <c r="I22" t="s">
+        <v>90</v>
+      </c>
+      <c r="J22" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23">
         <v>1001</v>
       </c>
@@ -1934,22 +2031,187 @@
         <v>0</v>
       </c>
       <c r="C23">
+        <v>20023</v>
+      </c>
+      <c r="D23" t="s">
+        <v>91</v>
+      </c>
+      <c r="E23" t="s">
+        <v>92</v>
+      </c>
+      <c r="F23">
+        <v>2001</v>
+      </c>
+      <c r="G23" t="s">
+        <v>82</v>
+      </c>
+      <c r="H23" t="s">
+        <v>93</v>
+      </c>
+      <c r="I23" t="s">
+        <v>90</v>
+      </c>
+      <c r="J23" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24">
+        <v>1001</v>
+      </c>
+      <c r="B24" t="b">
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <v>20024</v>
+      </c>
+      <c r="D24" t="s">
+        <v>94</v>
+      </c>
+      <c r="E24" t="s">
+        <v>95</v>
+      </c>
+      <c r="F24">
+        <v>2001</v>
+      </c>
+      <c r="G24" t="s">
+        <v>82</v>
+      </c>
+      <c r="H24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I24" t="s">
+        <v>90</v>
+      </c>
+      <c r="J24" t="s">
+        <v>83</v>
+      </c>
+      <c r="K24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25">
+        <v>1001</v>
+      </c>
+      <c r="B25" t="b">
+        <v>0</v>
+      </c>
+      <c r="C25">
+        <v>20031</v>
+      </c>
+      <c r="D25" t="s">
+        <v>96</v>
+      </c>
+      <c r="E25" t="s">
+        <v>97</v>
+      </c>
+      <c r="F25">
+        <v>2001</v>
+      </c>
+      <c r="G25" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26">
+        <v>1001</v>
+      </c>
+      <c r="B26" t="b">
+        <v>0</v>
+      </c>
+      <c r="C26">
+        <v>20032</v>
+      </c>
+      <c r="D26" t="s">
+        <v>98</v>
+      </c>
+      <c r="E26" t="s">
+        <v>99</v>
+      </c>
+      <c r="F26">
+        <v>2001</v>
+      </c>
+      <c r="G26" t="s">
+        <v>82</v>
+      </c>
+      <c r="H26" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27">
+        <v>1001</v>
+      </c>
+      <c r="B27" t="b">
+        <v>0</v>
+      </c>
+      <c r="C27">
+        <v>20033</v>
+      </c>
+      <c r="D27" t="s">
+        <v>100</v>
+      </c>
+      <c r="E27" t="s">
+        <v>101</v>
+      </c>
+      <c r="F27">
+        <v>2001</v>
+      </c>
+      <c r="G27" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
+      <c r="A28">
+        <v>1001</v>
+      </c>
+      <c r="B28" t="b">
+        <v>0</v>
+      </c>
+      <c r="C28">
+        <v>20034</v>
+      </c>
+      <c r="D28" t="s">
+        <v>102</v>
+      </c>
+      <c r="E28" t="s">
+        <v>103</v>
+      </c>
+      <c r="F28">
+        <v>2001</v>
+      </c>
+      <c r="G28" t="s">
+        <v>82</v>
+      </c>
+      <c r="H28" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
+      <c r="A29">
+        <v>1001</v>
+      </c>
+      <c r="B29" t="b">
+        <v>0</v>
+      </c>
+      <c r="C29">
         <v>2004</v>
       </c>
-      <c r="D23" t="s">
-        <v>81</v>
-      </c>
-      <c r="E23" t="s">
-        <v>82</v>
-      </c>
-      <c r="H23" t="s">
-        <v>31</v>
-      </c>
-      <c r="I23" t="s">
-        <v>30</v>
-      </c>
-      <c r="J23" t="s">
-        <v>60</v>
+      <c r="D29" t="s">
+        <v>104</v>
+      </c>
+      <c r="E29" t="s">
+        <v>105</v>
+      </c>
+      <c r="H29" t="s">
+        <v>37</v>
+      </c>
+      <c r="I29" t="s">
+        <v>36</v>
+      </c>
+      <c r="J29" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
